--- a/Assets/Data/Dungeon0073.xlsx
+++ b/Assets/Data/Dungeon0073.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -59,16 +59,19 @@
   <si>
     <t>Dr</t>
   </si>
+  <si>
+    <t>①</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -87,6 +90,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -102,8 +174,16 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -117,45 +197,22 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,62 +226,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,7 +242,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -251,25 +320,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,133 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,6 +420,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -430,6 +433,65 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,65 +533,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -538,145 +541,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,8 +1492,6 @@
       <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I6"/>
-      <c r="J6"/>
       <c r="K6" t="s">
         <v>11</v>
       </c>
@@ -1557,8 +1558,6 @@
         <v>9</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7"/>
-      <c r="K7"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
@@ -3572,13 +3571,19 @@
         <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="M3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>9</v>
@@ -3642,11 +3647,21 @@
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="N4" s="1" t="s">
         <v>9</v>
       </c>
@@ -3709,11 +3724,21 @@
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="N5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3776,13 +3801,21 @@
       <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1" t="s">
         <v>12</v>
@@ -3843,11 +3876,21 @@
       <c r="H7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="1"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="N7" s="1" t="s">
         <v>9</v>
       </c>
@@ -3910,11 +3953,21 @@
       <c r="H8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="N8" s="1" t="s">
         <v>9</v>
       </c>
@@ -3978,13 +4031,19 @@
         <v>9</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="M9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>9</v>
